--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -138,9 +138,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -382,7 +381,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1406,32 +1405,54 @@
         <v>0</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="12"/>
+      <c r="C13" s="12" t="n">
+        <v>6</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="G13" s="4"/>
-      <c r="H13" s="12"/>
+      <c r="H13" s="12" t="n">
+        <v>13</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="11"/>
+      <c r="K13" s="11" t="n">
+        <v>13</v>
+      </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="12"/>
+      <c r="M13" s="12" t="n">
+        <v>18</v>
+      </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="11" t="n">
+        <v>18</v>
+      </c>
       <c r="Q13" s="4"/>
-      <c r="R13" s="12"/>
+      <c r="R13" s="12" t="n">
+        <v>21</v>
+      </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
-      <c r="U13" s="11"/>
+      <c r="U13" s="11" t="n">
+        <v>26</v>
+      </c>
       <c r="V13" s="4"/>
-      <c r="W13" s="12"/>
+      <c r="W13" s="12" t="n">
+        <v>29</v>
+      </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="11"/>
+      <c r="Z13" s="11" t="n">
+        <v>29</v>
+      </c>
       <c r="AA13" s="4"/>
-      <c r="AB13" s="12"/>
+      <c r="AB13" s="12" t="n">
+        <v>38</v>
+      </c>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
     </row>
@@ -1479,16 +1500,14 @@
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B15" s="15" t="n">
-        <f aca="false">C16-C13</f>
         <v>0</v>
       </c>
       <c r="C15" s="15" t="n">
-        <f aca="false">MIN(F13,F19)-C13</f>
         <v>0</v>
       </c>
       <c r="D15" s="16"/>
@@ -1497,39 +1516,57 @@
         <f aca="false" t="array" ref="F15:F15">VLOOKUP(F14,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="G15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="14" t="n">
         <f aca="false" t="array" ref="K15:K15">VLOOKUP(K14,$A$2:$H$10,8)</f>
         <v>5</v>
       </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
+      <c r="L15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="14" t="n">
         <f aca="false" t="array" ref="P15:P15">VLOOKUP(P14,$A$2:$H$10,8)</f>
         <v>3</v>
       </c>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
+      <c r="Q15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="S15" s="17"/>
       <c r="T15" s="18"/>
       <c r="U15" s="14" t="n">
         <f aca="false" t="array" ref="U15:U15">VLOOKUP(U14,$A$2:$H$10,8)</f>
         <v>3</v>
       </c>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
+      <c r="V15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="X15" s="17"/>
       <c r="Y15" s="17"/>
       <c r="Z15" s="14" t="n">
         <f aca="false" t="array" ref="Z15:Z15">VLOOKUP(Z14,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="AA15" s="15"/>
+      <c r="AA15" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="AB15" s="15"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
@@ -1539,32 +1576,54 @@
         <v>0</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="20"/>
+      <c r="C16" s="20" t="n">
+        <v>6</v>
+      </c>
       <c r="D16" s="21"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="19"/>
+      <c r="F16" s="19" t="n">
+        <v>11</v>
+      </c>
       <c r="G16" s="4"/>
-      <c r="H16" s="20"/>
+      <c r="H16" s="20" t="n">
+        <v>18</v>
+      </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="19"/>
+      <c r="K16" s="19" t="n">
+        <v>18</v>
+      </c>
       <c r="L16" s="4"/>
-      <c r="M16" s="20"/>
+      <c r="M16" s="20" t="n">
+        <v>23</v>
+      </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="19"/>
+      <c r="P16" s="19" t="n">
+        <v>23</v>
+      </c>
       <c r="Q16" s="4"/>
-      <c r="R16" s="20"/>
+      <c r="R16" s="20" t="n">
+        <v>26</v>
+      </c>
       <c r="S16" s="4"/>
       <c r="T16" s="22"/>
-      <c r="U16" s="19"/>
+      <c r="U16" s="19" t="n">
+        <v>26</v>
+      </c>
       <c r="V16" s="4"/>
-      <c r="W16" s="20"/>
+      <c r="W16" s="20" t="n">
+        <v>29</v>
+      </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-      <c r="Z16" s="19"/>
+      <c r="Z16" s="19" t="n">
+        <v>29</v>
+      </c>
       <c r="AA16" s="4"/>
-      <c r="AB16" s="20"/>
+      <c r="AB16" s="20" t="n">
+        <v>38</v>
+      </c>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
     </row>
@@ -1587,15 +1646,27 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="23"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="12"/>
-      <c r="K19" s="11"/>
+      <c r="H19" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="L19" s="4"/>
-      <c r="M19" s="12"/>
-      <c r="P19" s="11"/>
+      <c r="M19" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>19</v>
+      </c>
       <c r="Q19" s="4"/>
-      <c r="R19" s="12"/>
+      <c r="R19" s="12" t="n">
+        <v>26</v>
+      </c>
       <c r="T19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1623,36 +1694,60 @@
         <f aca="false" t="array" ref="F21:F21">VLOOKUP(F20,$A$2:$H$10,8)</f>
         <v>4</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
+      <c r="G21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="14" t="n">
         <f aca="false" t="array" ref="K21:K21">VLOOKUP(K20,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
+      <c r="L21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="14" t="n">
         <f aca="false" t="array" ref="P21:P21">VLOOKUP(P20,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
+      <c r="Q21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="S21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="19"/>
+      <c r="F22" s="19" t="n">
+        <v>6</v>
+      </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="20"/>
-      <c r="K22" s="19"/>
+      <c r="H22" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="L22" s="4"/>
-      <c r="M22" s="20"/>
-      <c r="P22" s="19"/>
+      <c r="M22" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P22" s="19" t="n">
+        <v>19</v>
+      </c>
       <c r="Q22" s="4"/>
-      <c r="R22" s="20"/>
+      <c r="R22" s="20" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="1" state="visible" r:id="rId2"/>
@@ -197,7 +197,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,13 +213,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFD7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -320,7 +326,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -431,6 +437,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -553,7 +571,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFFFD7"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -586,13 +604,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>116640</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>75960</xdr:rowOff>
+      <xdr:rowOff>68400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>266400</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>75960</xdr:rowOff>
+      <xdr:rowOff>68400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2003,20 +2021,20 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="28" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2119,16 +2137,30 @@
         <v>0</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="12"/>
-      <c r="F9" s="11"/>
+      <c r="C9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="12"/>
-      <c r="K9" s="11"/>
+      <c r="H9" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>13</v>
+      </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="12"/>
-      <c r="P9" s="11"/>
+      <c r="M9" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>18</v>
+      </c>
       <c r="Q9" s="4"/>
-      <c r="R9" s="12"/>
+      <c r="R9" s="12" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
@@ -2157,45 +2189,79 @@
         <f aca="false" t="array" ref="A11:A11">VLOOKUP(A10,$A$2:$H$10,8)</f>
         <v>6</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="F11" s="14" t="n">
         <f aca="false" t="array" ref="F11:F11">VLOOKUP(F10,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="G11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" s="14" t="n">
         <f aca="false" t="array" ref="K11:K11">VLOOKUP(K10,$A$2:$H$10,8)</f>
         <v>5</v>
       </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
+      <c r="L11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" s="14" t="n">
         <f aca="false" t="array" ref="P11:P11">VLOOKUP(P10,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="Q11" s="15"/>
+      <c r="Q11" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="R11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19"/>
+      <c r="A12" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="20"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>6</v>
+      </c>
       <c r="G12" s="4"/>
-      <c r="H12" s="20"/>
-      <c r="K12" s="19"/>
+      <c r="H12" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>13</v>
+      </c>
       <c r="L12" s="4"/>
-      <c r="M12" s="20"/>
-      <c r="P12" s="19"/>
+      <c r="M12" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="P12" s="19" t="n">
+        <v>18</v>
+      </c>
       <c r="Q12" s="4"/>
-      <c r="R12" s="20"/>
+      <c r="R12" s="20" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="11"/>
+      <c r="F15" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="G15" s="4"/>
-      <c r="H15" s="12"/>
+      <c r="H15" s="12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F16" s="13" t="s">
@@ -2204,260 +2270,268 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F17" s="14" t="n">
         <f aca="false" t="array" ref="F17:F17">VLOOKUP(F16,$A$2:$H$10,8)</f>
         <v>4</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+      <c r="G17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="19"/>
+      <c r="F18" s="19" t="n">
+        <v>9</v>
+      </c>
       <c r="G18" s="4"/>
-      <c r="H18" s="20"/>
+      <c r="H18" s="20" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="28"/>
-      <c r="B51" s="30" t="s">
+      <c r="A51" s="31"/>
+      <c r="B51" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30" t="s">
+      <c r="C51" s="33"/>
+      <c r="D51" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="29"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="32"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28"/>
-      <c r="B52" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="32" t="s">
+      <c r="A52" s="31"/>
+      <c r="B52" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="29"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="32"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="28"/>
-      <c r="B53" s="33" t="s">
+      <c r="A53" s="31"/>
+      <c r="B53" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="D53" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="30"/>
-      <c r="J53" s="30"/>
-      <c r="K53" s="30"/>
-      <c r="L53" s="29"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33"/>
+      <c r="I53" s="33"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="32"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="28"/>
-      <c r="B54" s="30" t="s">
+      <c r="A54" s="31"/>
+      <c r="B54" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30" t="s">
+      <c r="C54" s="33"/>
+      <c r="D54" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="29"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="32"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="28"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="29"/>
+      <c r="A55" s="31"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="33"/>
+      <c r="L55" s="32"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28"/>
-      <c r="B56" s="35" t="s">
+      <c r="A56" s="31"/>
+      <c r="B56" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="C56" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="29"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+      <c r="L56" s="32"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="28"/>
-      <c r="B57" s="35" t="s">
+      <c r="A57" s="31"/>
+      <c r="B57" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
-      <c r="H57" s="36"/>
-      <c r="I57" s="36"/>
-      <c r="J57" s="36"/>
-      <c r="K57" s="36"/>
-      <c r="L57" s="29"/>
+      <c r="D57" s="39"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="39"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="39"/>
+      <c r="K57" s="39"/>
+      <c r="L57" s="32"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="28"/>
-      <c r="B58" s="35" t="s">
+      <c r="A58" s="31"/>
+      <c r="B58" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="36" t="s">
+      <c r="C58" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="36"/>
-      <c r="K58" s="36"/>
-      <c r="L58" s="29"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="39"/>
+      <c r="L58" s="32"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="28"/>
-      <c r="B59" s="35" t="s">
+      <c r="A59" s="31"/>
+      <c r="B59" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="C59" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
-      <c r="L59" s="29"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="39"/>
+      <c r="K59" s="39"/>
+      <c r="L59" s="32"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="28"/>
-      <c r="B60" s="33" t="s">
+      <c r="A60" s="31"/>
+      <c r="B60" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="36" t="s">
+      <c r="C60" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="36"/>
-      <c r="K60" s="36"/>
-      <c r="L60" s="29"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="32"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="28"/>
-      <c r="B61" s="34" t="s">
+      <c r="A61" s="31"/>
+      <c r="B61" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="36" t="s">
+      <c r="C61" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="36"/>
-      <c r="L61" s="29"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
+      <c r="K61" s="39"/>
+      <c r="L61" s="32"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="28"/>
-      <c r="B62" s="37" t="s">
+      <c r="A62" s="31"/>
+      <c r="B62" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="29"/>
-      <c r="K62" s="29"/>
-      <c r="L62" s="29"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="32"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="28"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
+      <c r="A63" s="31"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="1" state="visible" r:id="rId2"/>
@@ -141,7 +141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -178,6 +178,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Alegreya Sans"/>
       <family val="3"/>
@@ -197,7 +205,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,6 +234,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFD7"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor rgb="FFFFFFD7"/>
       </patternFill>
     </fill>
   </fills>
@@ -326,7 +340,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -451,6 +465,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -463,23 +481,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -555,7 +573,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8E8E8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -602,15 +620,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>116640</xdr:colOff>
+      <xdr:colOff>117000</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>68400</xdr:rowOff>
+      <xdr:rowOff>68760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>266400</xdr:colOff>
+      <xdr:colOff>266760</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>68400</xdr:rowOff>
+      <xdr:rowOff>68760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -619,7 +637,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1198440" y="8203680"/>
+          <a:off x="1198800" y="8196480"/>
           <a:ext cx="1773000" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -647,13 +665,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>360</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>271080</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -662,7 +680,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="811800" y="1628280"/>
+          <a:off x="811800" y="1628640"/>
           <a:ext cx="541080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -689,13 +707,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>360</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>271080</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -704,7 +722,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2164320" y="1628280"/>
+          <a:off x="2164320" y="1628640"/>
           <a:ext cx="541080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -731,13 +749,13 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>360</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>271080</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -746,7 +764,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3516840" y="1628280"/>
+          <a:off x="3516840" y="1628640"/>
           <a:ext cx="541080" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -773,13 +791,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>264600</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2520</xdr:rowOff>
+      <xdr:rowOff>2880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>271080</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2520</xdr:rowOff>
+      <xdr:rowOff>2880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -788,7 +806,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1076040" y="2603160"/>
+          <a:off x="1076040" y="2603520"/>
           <a:ext cx="276840" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -815,13 +833,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>360</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2160</xdr:rowOff>
+      <xdr:rowOff>2520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>6840</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2160</xdr:rowOff>
+      <xdr:rowOff>2520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -830,7 +848,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2164320" y="2602800"/>
+          <a:off x="2164320" y="2603160"/>
           <a:ext cx="276840" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -855,15 +873,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1080</xdr:colOff>
+      <xdr:colOff>1440</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1080</xdr:rowOff>
+      <xdr:rowOff>1440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>7560</xdr:colOff>
+      <xdr:colOff>7920</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>18360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -872,7 +890,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1082880" y="1626480"/>
+          <a:off x="1083240" y="1626840"/>
           <a:ext cx="6480" cy="992160"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -897,15 +915,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1080</xdr:colOff>
+      <xdr:colOff>1440</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
+      <xdr:rowOff>720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>7560</xdr:colOff>
+      <xdr:colOff>7920</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>17640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -914,7 +932,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2435400" y="1625760"/>
+          <a:off x="2435760" y="1626120"/>
           <a:ext cx="6480" cy="992160"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -945,7 +963,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AD45"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="0" width="3.83"/>
   </cols>
@@ -1423,54 +1441,32 @@
         <v>0</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="12" t="n">
-        <v>6</v>
-      </c>
+      <c r="C13" s="12"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="F13" s="11"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="12" t="n">
-        <v>13</v>
-      </c>
+      <c r="H13" s="12"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="11" t="n">
-        <v>13</v>
-      </c>
+      <c r="K13" s="11"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="12" t="n">
-        <v>18</v>
-      </c>
+      <c r="M13" s="12"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
-      <c r="P13" s="11" t="n">
-        <v>18</v>
-      </c>
+      <c r="P13" s="11"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="12" t="n">
-        <v>21</v>
-      </c>
+      <c r="R13" s="12"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
-      <c r="U13" s="11" t="n">
-        <v>26</v>
-      </c>
+      <c r="U13" s="11"/>
       <c r="V13" s="4"/>
-      <c r="W13" s="12" t="n">
-        <v>29</v>
-      </c>
+      <c r="W13" s="12"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="11" t="n">
-        <v>29</v>
-      </c>
+      <c r="Z13" s="11"/>
       <c r="AA13" s="4"/>
-      <c r="AB13" s="12" t="n">
-        <v>38</v>
-      </c>
+      <c r="AB13" s="12"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
     </row>
@@ -1518,73 +1514,51 @@
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
       <c r="D15" s="16"/>
       <c r="E15" s="17"/>
       <c r="F15" s="14" t="n">
         <f aca="false" t="array" ref="F15:F15">VLOOKUP(F14,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="14" t="n">
         <f aca="false" t="array" ref="K15:K15">VLOOKUP(K14,$A$2:$H$10,8)</f>
         <v>5</v>
       </c>
-      <c r="L15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="14" t="n">
         <f aca="false" t="array" ref="P15:P15">VLOOKUP(P14,$A$2:$H$10,8)</f>
         <v>3</v>
       </c>
-      <c r="Q15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" s="15" t="n">
-        <v>5</v>
-      </c>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
       <c r="S15" s="17"/>
       <c r="T15" s="18"/>
       <c r="U15" s="14" t="n">
         <f aca="false" t="array" ref="U15:U15">VLOOKUP(U14,$A$2:$H$10,8)</f>
         <v>3</v>
       </c>
-      <c r="V15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
       <c r="X15" s="17"/>
       <c r="Y15" s="17"/>
       <c r="Z15" s="14" t="n">
         <f aca="false" t="array" ref="Z15:Z15">VLOOKUP(Z14,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="AA15" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA15" s="15"/>
       <c r="AB15" s="15"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
@@ -1594,54 +1568,32 @@
         <v>0</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="20" t="n">
-        <v>6</v>
-      </c>
+      <c r="C16" s="20"/>
       <c r="D16" s="21"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="19" t="n">
-        <v>11</v>
-      </c>
+      <c r="F16" s="19"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="20" t="n">
-        <v>18</v>
-      </c>
+      <c r="H16" s="20"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="19" t="n">
-        <v>18</v>
-      </c>
+      <c r="K16" s="19"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="20" t="n">
-        <v>23</v>
-      </c>
+      <c r="M16" s="20"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="19" t="n">
-        <v>23</v>
-      </c>
+      <c r="P16" s="19"/>
       <c r="Q16" s="4"/>
-      <c r="R16" s="20" t="n">
-        <v>26</v>
-      </c>
+      <c r="R16" s="20"/>
       <c r="S16" s="4"/>
       <c r="T16" s="22"/>
-      <c r="U16" s="19" t="n">
-        <v>26</v>
-      </c>
+      <c r="U16" s="19"/>
       <c r="V16" s="4"/>
-      <c r="W16" s="20" t="n">
-        <v>29</v>
-      </c>
+      <c r="W16" s="20"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-      <c r="Z16" s="19" t="n">
-        <v>29</v>
-      </c>
+      <c r="Z16" s="19"/>
       <c r="AA16" s="4"/>
-      <c r="AB16" s="20" t="n">
-        <v>38</v>
-      </c>
+      <c r="AB16" s="20"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
     </row>
@@ -1664,27 +1616,15 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="23"/>
-      <c r="F19" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="F19" s="11"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>10</v>
-      </c>
+      <c r="H19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>19</v>
-      </c>
+      <c r="M19" s="12"/>
+      <c r="P19" s="11"/>
       <c r="Q19" s="4"/>
-      <c r="R19" s="12" t="n">
-        <v>26</v>
-      </c>
+      <c r="R19" s="12"/>
       <c r="T19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1712,60 +1652,36 @@
         <f aca="false" t="array" ref="F21:F21">VLOOKUP(F20,$A$2:$H$10,8)</f>
         <v>4</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="14" t="n">
         <f aca="false" t="array" ref="K21:K21">VLOOKUP(K20,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="L21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
       <c r="N21" s="17"/>
       <c r="O21" s="17"/>
       <c r="P21" s="14" t="n">
         <f aca="false" t="array" ref="P21:P21">VLOOKUP(P20,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="Q21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
       <c r="S21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="19" t="n">
-        <v>6</v>
-      </c>
+      <c r="F22" s="19"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>10</v>
-      </c>
+      <c r="H22" s="20"/>
+      <c r="K22" s="19"/>
       <c r="L22" s="4"/>
-      <c r="M22" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="P22" s="19" t="n">
-        <v>19</v>
-      </c>
+      <c r="M22" s="20"/>
+      <c r="P22" s="19"/>
       <c r="Q22" s="4"/>
-      <c r="R22" s="20" t="n">
-        <v>26</v>
-      </c>
+      <c r="R22" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1994,7 +1910,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15 G15 L15 Q15 V15 AA15 Q21 L21 G21">
+  <conditionalFormatting sqref="B15 G15 L15 G21 Q15 L21 Q21 V15 AA15">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2015,7 +1931,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R63"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="0" width="3.83"/>
   </cols>
@@ -2137,30 +2053,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="C9" s="12"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>13</v>
-      </c>
+      <c r="H9" s="12"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="P9" s="11" t="n">
-        <v>18</v>
-      </c>
+      <c r="M9" s="12"/>
+      <c r="P9" s="11"/>
       <c r="Q9" s="4"/>
-      <c r="R9" s="12" t="n">
-        <v>27</v>
-      </c>
+      <c r="R9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
@@ -2189,79 +2091,47 @@
         <f aca="false" t="array" ref="A11:A11">VLOOKUP(A10,$A$2:$H$10,8)</f>
         <v>6</v>
       </c>
-      <c r="B11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="14"/>
       <c r="F11" s="14" t="n">
         <f aca="false" t="array" ref="F11:F11">VLOOKUP(F10,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="G11" s="31"/>
+      <c r="H11" s="14"/>
       <c r="K11" s="14" t="n">
         <f aca="false" t="array" ref="K11:K11">VLOOKUP(K10,$A$2:$H$10,8)</f>
         <v>5</v>
       </c>
-      <c r="L11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="L11" s="31"/>
+      <c r="M11" s="14"/>
       <c r="P11" s="14" t="n">
         <f aca="false" t="array" ref="P11:P11">VLOOKUP(P10,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="Q11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="15"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="n">
         <v>0</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>6</v>
-      </c>
+      <c r="C12" s="20"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>13</v>
-      </c>
+      <c r="H12" s="20"/>
+      <c r="K12" s="19"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="P12" s="19" t="n">
-        <v>18</v>
-      </c>
+      <c r="M12" s="20"/>
+      <c r="P12" s="19"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="20" t="n">
-        <v>27</v>
-      </c>
+      <c r="R12" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="11" t="n">
-        <v>6</v>
-      </c>
+      <c r="F15" s="11"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="12" t="n">
-        <v>10</v>
-      </c>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F16" s="13" t="s">
@@ -2270,268 +2140,260 @@
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F17" s="14" t="n">
         <f aca="false" t="array" ref="F17:F17">VLOOKUP(F16,$A$2:$H$10,8)</f>
         <v>4</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="31"/>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="19"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="32"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="32"/>
+      <c r="B51" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="33"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="32"/>
+      <c r="B52" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="33"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="32"/>
+      <c r="B53" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="C53" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="33"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="32"/>
+      <c r="B54" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="33"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="32"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="33"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="32"/>
+      <c r="B56" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="33"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="32"/>
+      <c r="B57" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="33"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="32"/>
+      <c r="B58" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="33"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="32"/>
+      <c r="B59" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="33"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="32"/>
+      <c r="B60" s="37" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="20" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="31"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="31"/>
-      <c r="B51" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="32"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="31"/>
-      <c r="B52" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="32"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="31"/>
-      <c r="B53" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="37" t="s">
+      <c r="C60" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="33"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="32"/>
+      <c r="B61" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="36" t="s">
+      <c r="C61" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="33"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="32"/>
+      <c r="B62" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="32"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="31"/>
-      <c r="B54" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="32"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="31"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="32"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="31"/>
-      <c r="B56" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="32"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="31"/>
-      <c r="B57" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="39"/>
-      <c r="G57" s="39"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39"/>
-      <c r="K57" s="39"/>
-      <c r="L57" s="32"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="31"/>
-      <c r="B58" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="32"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="31"/>
-      <c r="B59" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C59" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="32"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="31"/>
-      <c r="B60" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="32"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="31"/>
-      <c r="B61" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
-      <c r="L61" s="32"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="31"/>
-      <c r="B62" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" s="32" t="s">
+      <c r="C62" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="31"/>
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2556,7 +2418,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11 G11 G17 L11 Q11">
+  <conditionalFormatting sqref="B11 G11 L11 Q11 G17">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="40">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">E</t>
   </si>
   <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
     <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H</t>
   </si>
   <si>
     <t xml:space="preserve">G</t>
@@ -217,7 +217,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,6 +228,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -352,7 +358,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -393,43 +399,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -441,8 +451,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -477,7 +491,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -485,27 +499,27 @@
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -513,7 +527,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -521,15 +535,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -537,7 +551,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -994,7 +1008,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AG44"/>
   <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="3.83"/>
@@ -1075,25 +1089,20 @@
         <v>6</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="11" t="n">
-        <f aca="false">H2/(I2*J2)</f>
-        <v>3</v>
+        <f aca="false">ROUNDUP(H2/(I2*J2),0)</f>
+        <v>6</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
@@ -1127,23 +1136,18 @@
       <c r="I3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="10" t="n">
-        <v>0.8</v>
+      <c r="J3" s="14" t="n">
+        <v>0.35</v>
       </c>
       <c r="K3" s="11" t="n">
-        <f aca="false">H3/(I3*J3)</f>
-        <v>8.75</v>
+        <f aca="false">ROUNDUP(H3/(I3*J3),0)</f>
+        <v>20</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
@@ -1175,26 +1179,20 @@
         <v>4</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <f aca="false">(100%+20%)/2</f>
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0.65</v>
       </c>
       <c r="K4" s="11" t="n">
-        <f aca="false">H4/(I4*J4)</f>
-        <v>3.33333333333333</v>
+        <f aca="false">ROUNDUP(H4/(I4*J4),0)</f>
+        <v>7</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
@@ -1210,10 +1208,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="13"/>
@@ -1223,17 +1221,17 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="10" t="n">
-        <v>0.8</v>
+      <c r="J5" s="14" t="n">
+        <v>0.7</v>
       </c>
       <c r="K5" s="11" t="n">
-        <f aca="false">H5/(I5*J5)</f>
-        <v>6.25</v>
+        <f aca="false">ROUNDUP(H5/(I5*J5),0)</f>
+        <v>13</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -1260,31 +1258,30 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="13"/>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="10" t="n">
-        <f aca="false">(100%+20%)/2</f>
-        <v>0.6</v>
+      <c r="J6" s="14" t="n">
+        <v>0.35</v>
       </c>
       <c r="K6" s="11" t="n">
-        <f aca="false">H6/(I6*J6)</f>
-        <v>15</v>
+        <f aca="false">ROUNDUP(H6/(I6*J6),0)</f>
+        <v>9</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1311,15 +1308,15 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="13"/>
       <c r="E7" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -1330,11 +1327,11 @@
         <v>1</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <f aca="false">H7/(I7*J7)</f>
-        <v>3.75</v>
+        <f aca="false">ROUNDUP(H7/(I7*J7),0)</f>
+        <v>3</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -1361,10 +1358,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="13"/>
@@ -1374,17 +1371,17 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="J8" s="14" t="n">
+        <v>0.65</v>
+      </c>
       <c r="K8" s="11" t="n">
-        <f aca="false">H8/(I8*J8)</f>
-        <v>1.5</v>
+        <f aca="false">ROUNDUP(H8/(I8*J8),0)</f>
+        <v>11</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -1411,31 +1408,30 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="D9" s="13"/>
-      <c r="E9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
       <c r="H9" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="10" t="n">
-        <f aca="false">(100%+20%)/2</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <f aca="false">H9/(I9*J9)</f>
-        <v>11.6666666666667</v>
+        <f aca="false">ROUNDUP(H9/(I9*J9),0)</f>
+        <v>9</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1461,32 +1457,17 @@
       <c r="AG9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <f aca="false">H10/(I10*J10)</f>
-        <v>4.5</v>
-      </c>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -1506,9 +1487,6 @@
       <c r="AB10" s="5"/>
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="5"/>
-      <c r="AG10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -1520,11 +1498,6 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
@@ -1543,413 +1516,351 @@
       <c r="AD11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
+      <c r="A12" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="16" t="n">
+        <f aca="false">A12+A14</f>
+        <v>6</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="15" t="n">
+        <f aca="false">C12</f>
+        <v>6</v>
+      </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="H12" s="16" t="n">
+        <f aca="false">F12+F14</f>
+        <v>26</v>
+      </c>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="P12" s="15" t="n">
+        <f aca="false">H12</f>
+        <v>26</v>
+      </c>
       <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
+      <c r="R12" s="16" t="n">
+        <f aca="false">P12+P14</f>
+        <v>35</v>
+      </c>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
+      <c r="U12" s="15" t="n">
+        <f aca="false">MAX(R18,R12)</f>
+        <v>37</v>
+      </c>
       <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
+      <c r="W12" s="16" t="n">
+        <f aca="false">U12+U14</f>
+        <v>40</v>
+      </c>
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
+      <c r="Z12" s="15" t="n">
+        <f aca="false">W12</f>
+        <v>40</v>
+      </c>
       <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
+      <c r="AB12" s="16" t="n">
+        <f aca="false">Z12+Z14</f>
+        <v>49</v>
+      </c>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="15" t="n">
-        <f aca="false">A13+A15</f>
-        <v>3</v>
-      </c>
+      <c r="A13" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="14" t="n">
-        <f aca="false">C13</f>
-        <v>3</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="15" t="n">
-        <f aca="false">F13+F15</f>
-        <v>11.75</v>
-      </c>
+      <c r="F13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="14" t="n">
-        <f aca="false">H13</f>
-        <v>11.75</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="15" t="n">
-        <f aca="false">K13+K15</f>
-        <v>18</v>
-      </c>
-      <c r="N13" s="5"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="14" t="n">
-        <f aca="false">M13</f>
-        <v>18</v>
-      </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="15" t="n">
-        <f aca="false">P13+P15</f>
-        <v>21.75</v>
-      </c>
+      <c r="P13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
-      <c r="U13" s="14" t="n">
-        <f aca="false">MAX(R19,R13)</f>
-        <v>33</v>
-      </c>
-      <c r="V13" s="5"/>
-      <c r="W13" s="15" t="n">
-        <f aca="false">U13+U15</f>
-        <v>34.5</v>
-      </c>
+      <c r="U13" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
-      <c r="Z13" s="14" t="n">
-        <f aca="false">W13</f>
-        <v>34.5</v>
-      </c>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="15" t="n">
-        <f aca="false">Z13+Z15</f>
-        <v>39</v>
-      </c>
+      <c r="Z13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
       <c r="AC13" s="5"/>
       <c r="AD13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="16" t="s">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="n">
+        <f aca="false">K2</f>
+        <v>6</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <f aca="false">C15-C12</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23" t="n">
+        <f aca="false">K3</f>
+        <v>20</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <f aca="false">H15-H12</f>
+        <v>2</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="23" t="n">
+        <f aca="false">K6</f>
         <v>9</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="16"/>
+      <c r="Q14" s="19" t="n">
+        <f aca="false">R15-R12</f>
+        <v>2</v>
+      </c>
+      <c r="R14" s="20"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="23" t="n">
+        <f aca="false">K7</f>
+        <v>3</v>
+      </c>
+      <c r="V14" s="19" t="n">
+        <f aca="false">W15-W12</f>
+        <v>0</v>
+      </c>
+      <c r="W14" s="20"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="23" t="n">
+        <f aca="false">K9</f>
+        <v>9</v>
+      </c>
+      <c r="AA14" s="19" t="n">
+        <f aca="false">AB15-AB12</f>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="20"/>
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="n">
-        <f aca="false">K2</f>
-        <v>3</v>
-      </c>
-      <c r="B15" s="18" t="n">
-        <f aca="false">C16-C13</f>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22" t="n">
-        <f aca="false">K3</f>
-        <v>8.75</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <f aca="false">H16-H13</f>
-        <v>11.25</v>
-      </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="22" t="n">
-        <f aca="false">K5</f>
-        <v>6.25</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <f aca="false">M16-M13</f>
-        <v>11.25</v>
-      </c>
-      <c r="M15" s="19"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="22" t="n">
-        <f aca="false">K7</f>
-        <v>3.75</v>
-      </c>
-      <c r="Q15" s="18" t="n">
-        <f aca="false">R16-R13</f>
-        <v>11.25</v>
-      </c>
-      <c r="R15" s="19"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="22" t="n">
-        <f aca="false">K8</f>
-        <v>1.5</v>
-      </c>
-      <c r="V15" s="18" t="n">
-        <f aca="false">W16-W13</f>
-        <v>0</v>
-      </c>
-      <c r="W15" s="19"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="22" t="n">
-        <f aca="false">K10</f>
-        <v>4.5</v>
-      </c>
-      <c r="AA15" s="18" t="n">
-        <f aca="false">AB16-AB13</f>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="19"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="27" t="n">
+        <f aca="false">MIN(F15,F21)</f>
+        <v>6</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="26" t="n">
+        <f aca="false">H15-F14</f>
+        <v>8</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="27" t="n">
+        <f aca="false">P15</f>
+        <v>28</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="26" t="n">
+        <f aca="false">R15-P14</f>
+        <v>28</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="27" t="n">
+        <f aca="false">U15</f>
+        <v>37</v>
+      </c>
+      <c r="S15" s="5"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="26" t="n">
+        <f aca="false">W15-U14</f>
+        <v>37</v>
+      </c>
+      <c r="V15" s="5"/>
+      <c r="W15" s="27" t="n">
+        <f aca="false">Z15</f>
+        <v>40</v>
+      </c>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="26" t="n">
+        <f aca="false">AB15-Z14</f>
+        <v>40</v>
+      </c>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="27" t="n">
+        <f aca="false">AB12</f>
+        <v>49</v>
+      </c>
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="n">
-        <v>0</v>
-      </c>
+      <c r="A16" s="5"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="25" t="n">
-        <f aca="false">MIN(F16,F22)</f>
-        <v>3</v>
-      </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="24" t="n">
-        <f aca="false">H16-F15</f>
-        <v>14.25</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="25" t="n">
-        <f aca="false">K16</f>
-        <v>23</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="24" t="n">
-        <f aca="false">M16-K15</f>
-        <v>23</v>
-      </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="25" t="n">
-        <f aca="false">P16</f>
-        <v>29.25</v>
-      </c>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="24" t="n">
-        <f aca="false">R16-P15</f>
-        <v>29.25</v>
-      </c>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="25" t="n">
-        <f aca="false">U16</f>
-        <v>33</v>
-      </c>
-      <c r="S16" s="5"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="24" t="n">
-        <f aca="false">W16-U15</f>
-        <v>33</v>
-      </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="25" t="n">
-        <f aca="false">Z16</f>
-        <v>34.5</v>
-      </c>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="24" t="n">
-        <f aca="false">AB16-Z15</f>
-        <v>34.5</v>
-      </c>
-      <c r="AA16" s="5"/>
-      <c r="AB16" s="25" t="n">
-        <f aca="false">AB13</f>
-        <v>39</v>
-      </c>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="30"/>
+      <c r="T16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="28"/>
-      <c r="T17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="T17" s="31"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="28"/>
-      <c r="T18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="F18" s="15" t="n">
+        <f aca="false">C12</f>
+        <v>6</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="16" t="n">
+        <f aca="false">F18+F20</f>
+        <v>13</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <f aca="false">H18</f>
+        <v>13</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="16" t="n">
+        <f aca="false">K18+K20</f>
+        <v>26</v>
+      </c>
+      <c r="P18" s="15" t="n">
+        <f aca="false">M18</f>
+        <v>26</v>
+      </c>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="16" t="n">
+        <f aca="false">P18+P20</f>
+        <v>37</v>
+      </c>
+      <c r="T18" s="31"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="28"/>
-      <c r="F19" s="14" t="n">
-        <f aca="false">C13</f>
-        <v>3</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="15" t="n">
-        <f aca="false">F19+F21</f>
-        <v>6.33333333333333</v>
-      </c>
-      <c r="K19" s="14" t="n">
-        <f aca="false">H19</f>
-        <v>6.33333333333333</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="15" t="n">
-        <f aca="false">K19+K21</f>
-        <v>21.3333333333333</v>
-      </c>
-      <c r="P19" s="14" t="n">
-        <f aca="false">M19</f>
-        <v>21.3333333333333</v>
-      </c>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="15" t="n">
-        <f aca="false">P19+P21</f>
-        <v>33</v>
-      </c>
-      <c r="T19" s="29"/>
+      <c r="D19" s="30"/>
+      <c r="F19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="K19" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="P19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="T19" s="31"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="28"/>
-      <c r="F20" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="K20" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="P20" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="T20" s="29"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23" t="n">
+        <f aca="false">K4</f>
+        <v>7</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <f aca="false">H21-H18</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23" t="n">
+        <f aca="false">K5</f>
+        <v>13</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <f aca="false">M21-M18</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="23" t="n">
+        <f aca="false">K8</f>
+        <v>11</v>
+      </c>
+      <c r="Q20" s="19" t="n">
+        <f aca="false">R21-R18</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="20"/>
+      <c r="S20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="21"/>
-      <c r="F21" s="22" t="n">
-        <f aca="false">K4</f>
-        <v>3.33333333333333</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <f aca="false">H22-H19</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="22" t="n">
-        <f aca="false">K6</f>
-        <v>15</v>
-      </c>
-      <c r="L21" s="18" t="n">
-        <f aca="false">M22-M19</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="22" t="n">
-        <f aca="false">K9</f>
-        <v>11.6666666666667</v>
-      </c>
-      <c r="Q21" s="18" t="n">
-        <f aca="false">R22-R19</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="19"/>
-      <c r="S21" s="21"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="24" t="n">
-        <f aca="false">H22-F21</f>
-        <v>3</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="25" t="n">
-        <f aca="false">K22</f>
-        <v>6.33333333333333</v>
-      </c>
-      <c r="K22" s="24" t="n">
-        <f aca="false">M22-K21</f>
-        <v>6.33333333333333</v>
-      </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="25" t="n">
-        <f aca="false">P22</f>
-        <v>21.3333333333333</v>
-      </c>
-      <c r="P22" s="24" t="n">
-        <f aca="false">R22-P21</f>
-        <v>21.3333333333333</v>
-      </c>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="25" t="n">
-        <f aca="false">U16</f>
-        <v>33</v>
-      </c>
+      <c r="F21" s="26" t="n">
+        <f aca="false">H21-F20</f>
+        <v>6</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="27" t="n">
+        <f aca="false">K21</f>
+        <v>13</v>
+      </c>
+      <c r="K21" s="26" t="n">
+        <f aca="false">M21-K20</f>
+        <v>13</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="27" t="n">
+        <f aca="false">P21</f>
+        <v>26</v>
+      </c>
+      <c r="P21" s="26" t="n">
+        <f aca="false">R21-P20</f>
+        <v>26</v>
+      </c>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="27" t="n">
+        <f aca="false">U15</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -1985,200 +1896,194 @@
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-      <c r="V31" s="5"/>
-      <c r="W31" s="5"/>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5"/>
-      <c r="Z31" s="5"/>
-      <c r="AA31" s="5"/>
-      <c r="AB31" s="5"/>
-      <c r="AC31" s="5"/>
-      <c r="AD31" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+      <c r="A33" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="30" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="s">
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B34" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C34" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D34" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="0" t="s">
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="30" t="s">
+      <c r="J34" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="0" t="s">
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="R35" s="30" t="s">
+      <c r="R34" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="S35" s="30"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+      <c r="Z34" s="32"/>
+      <c r="AA34" s="32"/>
+      <c r="AB34" s="32"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
+      <c r="A36" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>32</v>
-      </c>
+      <c r="A37" s="34"/>
+      <c r="C37" s="34"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="A38" s="34"/>
+      <c r="C38" s="34"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="32"/>
-      <c r="C39" s="32"/>
+      <c r="A39" s="34"/>
+      <c r="C39" s="34"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="32"/>
-      <c r="C40" s="32"/>
+      <c r="A40" s="34"/>
+      <c r="C40" s="34"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="32"/>
-      <c r="C41" s="32"/>
+      <c r="A41" s="34"/>
+      <c r="C41" s="34"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="32"/>
-      <c r="C42" s="32"/>
+      <c r="A42" s="34"/>
+      <c r="C42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="32"/>
-      <c r="C43" s="32"/>
+      <c r="A43" s="34"/>
+      <c r="C43" s="34"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="32"/>
-      <c r="C44" s="32"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="32"/>
-      <c r="C45" s="32"/>
+      <c r="A44" s="34"/>
+      <c r="C44" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="Z13:AB13"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="A33:C33"/>
     <mergeCell ref="D33:H33"/>
-    <mergeCell ref="A34:C34"/>
     <mergeCell ref="D34:H34"/>
+    <mergeCell ref="J34:P34"/>
+    <mergeCell ref="R34:AB34"/>
     <mergeCell ref="D35:H35"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="R35:AB35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="A37:A45"/>
-    <mergeCell ref="C37:C45"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="C36:C44"/>
   </mergeCells>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B34">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA15 V15 Q15 Q21 L15 L21 G21 G15 B15 H15:J10">
+  <conditionalFormatting sqref="AA14 V14 Q14 Q20 L20 G20 G14:J14 B14">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2205,20 +2110,20 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="33" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="35" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2317,351 +2222,351 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="15"/>
-      <c r="F9" s="14"/>
+      <c r="C9" s="16"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="15"/>
-      <c r="K9" s="14"/>
+      <c r="H9" s="16"/>
+      <c r="K9" s="15"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="15"/>
-      <c r="P9" s="14"/>
+      <c r="M9" s="16"/>
+      <c r="P9" s="15"/>
       <c r="Q9" s="5"/>
-      <c r="R9" s="15"/>
+      <c r="R9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="F10" s="16" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="F10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="K10" s="16" t="s">
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="K10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="P10" s="16" t="s">
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="P10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="23" t="n">
         <f aca="false" t="array" ref="A11:A11">VLOOKUP(A10,$A$2:$H$10,8)</f>
         <v>6</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="22"/>
-      <c r="F11" s="22" t="n">
+      <c r="B11" s="38"/>
+      <c r="C11" s="23"/>
+      <c r="F11" s="23" t="n">
         <f aca="false" t="array" ref="F11:F11">VLOOKUP(F10,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="22"/>
-      <c r="K11" s="22" t="n">
+      <c r="G11" s="38"/>
+      <c r="H11" s="23"/>
+      <c r="K11" s="23" t="n">
         <f aca="false" t="array" ref="K11:K11">VLOOKUP(K10,$A$2:$H$10,8)</f>
         <v>5</v>
       </c>
-      <c r="L11" s="36"/>
-      <c r="M11" s="22"/>
-      <c r="P11" s="22" t="n">
+      <c r="L11" s="38"/>
+      <c r="M11" s="23"/>
+      <c r="P11" s="23" t="n">
         <f aca="false" t="array" ref="P11:P11">VLOOKUP(P10,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="22"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="n">
+      <c r="A12" s="26" t="n">
         <v>0</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="25"/>
-      <c r="F12" s="24"/>
+      <c r="C12" s="27"/>
+      <c r="F12" s="26"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="25"/>
-      <c r="K12" s="24"/>
+      <c r="H12" s="27"/>
+      <c r="K12" s="26"/>
       <c r="L12" s="5"/>
-      <c r="M12" s="25"/>
-      <c r="P12" s="24"/>
+      <c r="M12" s="27"/>
+      <c r="P12" s="26"/>
       <c r="Q12" s="5"/>
-      <c r="R12" s="25"/>
+      <c r="R12" s="27"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="14"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="23" t="n">
         <f aca="false" t="array" ref="F17:F17">VLOOKUP(F16,$A$2:$H$10,8)</f>
         <v>4</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="22"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="24"/>
+      <c r="F18" s="26"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="25"/>
+      <c r="H18" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="37"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="38"/>
+      <c r="A50" s="39"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="37"/>
-      <c r="B51" s="39" t="s">
+      <c r="A51" s="39"/>
+      <c r="B51" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39" t="s">
+      <c r="C51" s="41"/>
+      <c r="D51" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="39"/>
-      <c r="J51" s="39"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="38"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="37"/>
-      <c r="B52" s="40" t="s">
+      <c r="A52" s="39"/>
+      <c r="B52" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="40"/>
-      <c r="D52" s="40"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="41" t="s">
+      <c r="C52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="38"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+      <c r="I52" s="43"/>
+      <c r="J52" s="43"/>
+      <c r="K52" s="41"/>
+      <c r="L52" s="40"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="37"/>
-      <c r="B53" s="42" t="s">
+      <c r="A53" s="39"/>
+      <c r="B53" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="43" t="s">
+      <c r="C53" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="42" t="s">
+      <c r="D53" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="38"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="40"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="37"/>
-      <c r="B54" s="39" t="s">
+      <c r="A54" s="39"/>
+      <c r="B54" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="39"/>
-      <c r="D54" s="39" t="s">
+      <c r="C54" s="41"/>
+      <c r="D54" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="38"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="40"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="37"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="38"/>
+      <c r="A55" s="39"/>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="40"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="37"/>
-      <c r="B56" s="44" t="s">
+      <c r="A56" s="39"/>
+      <c r="B56" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="45" t="s">
+      <c r="C56" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
-      <c r="K56" s="45"/>
-      <c r="L56" s="38"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="47"/>
+      <c r="K56" s="47"/>
+      <c r="L56" s="40"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="37"/>
-      <c r="B57" s="44" t="s">
+      <c r="A57" s="39"/>
+      <c r="B57" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="45"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
-      <c r="K57" s="45"/>
-      <c r="L57" s="38"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="47"/>
+      <c r="K57" s="47"/>
+      <c r="L57" s="40"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="37"/>
-      <c r="B58" s="44" t="s">
+      <c r="A58" s="39"/>
+      <c r="B58" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="45" t="s">
+      <c r="C58" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="45"/>
-      <c r="L58" s="38"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="47"/>
+      <c r="I58" s="47"/>
+      <c r="J58" s="47"/>
+      <c r="K58" s="47"/>
+      <c r="L58" s="40"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="37"/>
-      <c r="B59" s="44" t="s">
+      <c r="A59" s="39"/>
+      <c r="B59" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C59" s="45" t="s">
+      <c r="C59" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="45"/>
-      <c r="L59" s="38"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47"/>
+      <c r="H59" s="47"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="40"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="37"/>
-      <c r="B60" s="42" t="s">
+      <c r="A60" s="39"/>
+      <c r="B60" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C60" s="45" t="s">
+      <c r="C60" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D60" s="45"/>
-      <c r="E60" s="45"/>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="45"/>
-      <c r="K60" s="45"/>
-      <c r="L60" s="38"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47"/>
+      <c r="L60" s="40"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="37"/>
-      <c r="B61" s="43" t="s">
+      <c r="A61" s="39"/>
+      <c r="B61" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C61" s="45" t="s">
+      <c r="C61" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
-      <c r="L61" s="38"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47"/>
+      <c r="K61" s="47"/>
+      <c r="L61" s="40"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="37"/>
-      <c r="B62" s="46" t="s">
+      <c r="A62" s="39"/>
+      <c r="B62" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="38" t="s">
+      <c r="C62" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
-      <c r="L62" s="38"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
+      <c r="L62" s="40"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="37"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
-      <c r="L63" s="38"/>
+      <c r="A63" s="39"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="40"/>
+      <c r="L63" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle2" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="39">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -32,36 +32,45 @@
     <t xml:space="preserve">Nachfolger</t>
   </si>
   <si>
+    <t xml:space="preserve">Aufwand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapazität</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
     <t xml:space="preserve">D</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
   </si>
   <si>
     <t xml:space="preserve">E</t>
   </si>
   <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
     <t xml:space="preserve">H</t>
   </si>
   <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
     <t xml:space="preserve">FAZ</t>
   </si>
   <si>
@@ -123,9 +132,6 @@
   </si>
   <si>
     <t xml:space="preserve">Spätester Endzeitpunkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dauer</t>
   </si>
   <si>
     <t xml:space="preserve">Gesamter Puffer (SAZ–FAZ=SEZ–FEZ )</t>
@@ -206,14 +212,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFD7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFD7"/>
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -326,7 +332,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -347,35 +353,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,6 +381,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -427,6 +433,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -451,11 +461,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,7 +489,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -944,10 +954,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AD45"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AN45"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="0" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -964,395 +977,534 @@
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="I1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="L1" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
+      <c r="N1" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
+      <c r="S1" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
+      <c r="V1" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
+      <c r="X1" s="6" t="n">
+        <v>18</v>
+      </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
+      <c r="AA1" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
+      <c r="AC1" s="6" t="n">
+        <v>21</v>
+      </c>
       <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="1" t="n">
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="L2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
+      <c r="Q2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="V2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
+      <c r="AA2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
       <c r="AD2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG2" s="11"/>
+      <c r="AH2" s="11"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL2" s="11"/>
+      <c r="AM2" s="11"/>
+      <c r="AN2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="1" t="n">
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
+      <c r="L3" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="16"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="14" t="n">
+        <f aca="false">VLOOKUP(Q2,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="14" t="n">
+        <f aca="false">VLOOKUP(V2,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="14" t="n">
+        <f aca="false">VLOOKUP(AA2,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="AB3" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="14" t="n">
+        <f aca="false">VLOOKUP(AF2,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="14" t="n">
+        <f aca="false">VLOOKUP(AK2,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="L4" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+      <c r="N4" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" s="21"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="Q4" s="19" t="n">
+        <v>11</v>
+      </c>
       <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+      <c r="S4" s="20" t="n">
+        <v>18</v>
+      </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+      <c r="V4" s="19" t="n">
+        <v>18</v>
+      </c>
       <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+      <c r="X4" s="20" t="n">
+        <v>23</v>
+      </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="AA4" s="19" t="n">
+        <v>23</v>
+      </c>
       <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
+      <c r="AC4" s="20" t="n">
+        <v>26</v>
+      </c>
       <c r="AD4" s="4"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-      <c r="AD5" s="4"/>
+      <c r="O5" s="23"/>
+      <c r="AE5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
+      <c r="O6" s="23"/>
+      <c r="AE6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="O7" s="23"/>
+      <c r="Q7" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="S7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="X7" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
+      <c r="AC7" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="10"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="O8" s="23"/>
+      <c r="Q8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
-      <c r="AD8" s="4"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="V8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="AA8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
+      <c r="AE8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
       <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
-      <c r="AB9" s="4"/>
-      <c r="AC9" s="4"/>
-      <c r="AD9" s="4"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="14" t="n">
+        <f aca="false">VLOOKUP(Q8,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="14" t="n">
+        <f aca="false">VLOOKUP(V8,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="14" t="n">
+        <f aca="false">VLOOKUP(AA8,$A$2:$J$10,8)</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="Q10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" s="4"/>
+      <c r="S10" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="V10" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="X10" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA10" s="19" t="n">
+        <v>19</v>
+      </c>
       <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
+      <c r="AC10" s="20" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
@@ -1385,6 +1537,8 @@
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -1417,355 +1571,20 @@
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="V13" s="4"/>
-      <c r="W13" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
+      <c r="AF13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="13"/>
-      <c r="AC14" s="4"/>
-      <c r="AD14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="14" t="n">
-        <f aca="false" t="array" ref="F15:F15">VLOOKUP(F14,$A$2:$H$10,8)</f>
-        <v>7</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="14" t="n">
-        <f aca="false" t="array" ref="K15:K15">VLOOKUP(K14,$A$2:$H$10,8)</f>
-        <v>5</v>
-      </c>
-      <c r="L15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="14" t="n">
-        <f aca="false" t="array" ref="P15:P15">VLOOKUP(P14,$A$2:$H$10,8)</f>
-        <v>3</v>
-      </c>
-      <c r="Q15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="S15" s="17"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="14" t="n">
-        <f aca="false" t="array" ref="U15:U15">VLOOKUP(U14,$A$2:$H$10,8)</f>
-        <v>3</v>
-      </c>
-      <c r="V15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="14" t="n">
-        <f aca="false" t="array" ref="Z15:Z15">VLOOKUP(Z14,$A$2:$H$10,8)</f>
-        <v>9</v>
-      </c>
-      <c r="AA15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="15"/>
-      <c r="AC15" s="4"/>
-      <c r="AD15" s="4"/>
+      <c r="AF14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="S16" s="4"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="V16" s="4"/>
-      <c r="W16" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="23"/>
-      <c r="T17" s="24"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="23"/>
-      <c r="T18" s="24"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="23"/>
-      <c r="F19" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="T19" s="24"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="23"/>
-      <c r="F20" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="K20" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="P20" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="T20" s="24"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="17"/>
-      <c r="F21" s="14" t="n">
-        <f aca="false" t="array" ref="F21:F21">VLOOKUP(F20,$A$2:$H$10,8)</f>
-        <v>4</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="14" t="n">
-        <f aca="false" t="array" ref="K21:K21">VLOOKUP(K20,$A$2:$H$10,8)</f>
-        <v>9</v>
-      </c>
-      <c r="L21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="14" t="n">
-        <f aca="false" t="array" ref="P21:P21">VLOOKUP(P20,$A$2:$H$10,8)</f>
-        <v>7</v>
-      </c>
-      <c r="Q21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="P22" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="20" t="n">
-        <v>26</v>
-      </c>
+      <c r="AF16" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1833,169 +1652,174 @@
       <c r="AB31" s="4"/>
       <c r="AC31" s="4"/>
       <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>13</v>
+      <c r="A33" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
+      <c r="C33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="A34" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="0" t="s">
+      <c r="D35" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="R35" s="25" t="s">
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
+      <c r="L35" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="T35" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="U35" s="26"/>
+      <c r="V35" s="26"/>
+      <c r="W35" s="26"/>
+      <c r="X35" s="26"/>
+      <c r="Y35" s="26"/>
+      <c r="Z35" s="26"/>
+      <c r="AA35" s="26"/>
+      <c r="AB35" s="26"/>
+      <c r="AC35" s="26"/>
+      <c r="AD35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
+        <v>28</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>28</v>
+      <c r="A37" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="27"/>
-      <c r="C38" s="27"/>
+      <c r="A38" s="28"/>
+      <c r="C38" s="28"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="27"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="28"/>
+      <c r="C39" s="28"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="27"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="28"/>
+      <c r="C40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="27"/>
-      <c r="C41" s="27"/>
+      <c r="A41" s="28"/>
+      <c r="C41" s="28"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="27"/>
-      <c r="C42" s="27"/>
+      <c r="A42" s="28"/>
+      <c r="C42" s="28"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="27"/>
-      <c r="C43" s="27"/>
+      <c r="A43" s="28"/>
+      <c r="C43" s="28"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="A44" s="28"/>
+      <c r="C44" s="28"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="27"/>
-      <c r="C45" s="27"/>
+      <c r="A45" s="28"/>
+      <c r="C45" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="P14:R14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="AA8:AC8"/>
+    <mergeCell ref="D33:J33"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="R35:AB35"/>
-    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D34:J34"/>
+    <mergeCell ref="D35:J35"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="T35:AD35"/>
+    <mergeCell ref="D36:J36"/>
     <mergeCell ref="A37:A45"/>
     <mergeCell ref="C37:C45"/>
   </mergeCells>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B35 M3 R3 W3 AB3 AG3 AL3 AB9 W9 R9">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15 G15 L15 Q15 V15 AA15 Q21 L21 G21">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2015,174 +1839,174 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R63"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="0" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29" t="s">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="28" t="s">
-        <v>3</v>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="29" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="10"/>
       <c r="H2" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
       <c r="H3" s="1" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
       <c r="H4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
       <c r="H5" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
       <c r="H6" s="1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="5" t="n">
         <v>13</v>
       </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="5" t="n">
         <v>18</v>
       </c>
       <c r="Q9" s="4"/>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="6" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="F10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="K10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="P10" s="13" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="F10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="K10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="P10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="n">
@@ -2255,20 +2079,20 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G15" s="4"/>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="6" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="F16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F17" s="14" t="n">
@@ -2292,246 +2116,246 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="31"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="31"/>
-      <c r="B51" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="32"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="33"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="31"/>
-      <c r="B52" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="32"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="36"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="33"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="31"/>
-      <c r="B53" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="37" t="s">
+      <c r="A53" s="32"/>
+      <c r="B53" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="33"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="32"/>
+      <c r="B54" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="33"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="32"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="33"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="32"/>
+      <c r="B56" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="33"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="32"/>
+      <c r="B57" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="33"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="32"/>
+      <c r="B58" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D53" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="32"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="31"/>
-      <c r="B54" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="32"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="31"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="32"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="31"/>
-      <c r="B56" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="32"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="31"/>
-      <c r="B57" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="39"/>
-      <c r="G57" s="39"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="39"/>
-      <c r="K57" s="39"/>
-      <c r="L57" s="32"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="31"/>
-      <c r="B58" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="32"/>
+      <c r="C58" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="33"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="31"/>
-      <c r="B59" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C59" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="32"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="33"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="31"/>
-      <c r="B60" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39"/>
-      <c r="I60" s="39"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="32"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="33"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="31"/>
-      <c r="B61" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
-      <c r="L61" s="32"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="33"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="31"/>
-      <c r="B62" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="32"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="31"/>
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="32"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -144,8 +144,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00\ %"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -218,8 +220,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -230,8 +232,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFD7"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -332,11 +334,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -349,6 +355,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -357,7 +367,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -373,7 +387,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -385,35 +399,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -433,7 +459,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -449,16 +475,24 @@
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -959,841 +993,919 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="11" style="0" width="3.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="5" t="n">
+      <c r="K1" s="6"/>
+      <c r="L1" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="6" t="n">
+      <c r="M1" s="6"/>
+      <c r="N1" s="8" t="n">
+        <f aca="false">L3+L1</f>
         <v>6</v>
       </c>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="5" t="n">
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="7" t="n">
+        <f aca="false">N1</f>
         <v>6</v>
       </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="6" t="n">
+      <c r="R1" s="6"/>
+      <c r="S1" s="8" t="n">
+        <f aca="false">Q3+Q1</f>
+        <v>34</v>
+      </c>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="7" t="n">
+        <f aca="false">S1</f>
+        <v>34</v>
+      </c>
+      <c r="W1" s="6"/>
+      <c r="X1" s="8" t="n">
+        <f aca="false">V3+V1</f>
+        <v>54</v>
+      </c>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="7" t="n">
+        <f aca="false">X1</f>
+        <v>54</v>
+      </c>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="8" t="n">
+        <f aca="false">AA3+AA1</f>
+        <v>66</v>
+      </c>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="7" t="n">
+        <f aca="false">MAX(AC1,AC7)</f>
+        <v>66</v>
+      </c>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="8" t="n">
+        <f aca="false">AF3+AF1</f>
+        <v>69</v>
+      </c>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="7" t="n">
+        <f aca="false">AH1</f>
+        <v>69</v>
+      </c>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="8" t="n">
+        <f aca="false">AK3+AK1</f>
+        <v>78</v>
+      </c>
+      <c r="AN1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <f aca="false">ROUNDUP(H2/I2,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K2" s="6"/>
+      <c r="L2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="5" t="n">
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <f aca="false">ROUNDUP(H3/I3,0)</f>
+        <v>28</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="19" t="n">
+        <f aca="false">J2</f>
+        <v>6</v>
+      </c>
+      <c r="M3" s="20" t="n">
+        <f aca="false">N4-N1</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="21"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="19" t="n">
+        <f aca="false">J3</f>
+        <v>28</v>
+      </c>
+      <c r="R3" s="20" t="n">
+        <f aca="false">S4-S1</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="21"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="19" t="n">
+        <f aca="false">J5</f>
+        <v>20</v>
+      </c>
+      <c r="W3" s="20" t="n">
+        <f aca="false">X4-X1</f>
+        <v>0</v>
+      </c>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="19" t="n">
+        <f aca="false">J7</f>
+        <v>12</v>
+      </c>
+      <c r="AB3" s="20" t="n">
+        <f aca="false">AC4-AC1</f>
+        <v>0</v>
+      </c>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="19" t="n">
+        <f aca="false">J8</f>
+        <v>3</v>
+      </c>
+      <c r="AG3" s="20" t="n">
+        <f aca="false">AH4-AH1</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="19" t="n">
+        <f aca="false">J10</f>
+        <v>9</v>
+      </c>
+      <c r="AL3" s="20" t="n">
+        <f aca="false">AM4-AM1</f>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="21"/>
+      <c r="AN3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <f aca="false">100%-I3</f>
+        <v>0.75</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <f aca="false">ROUNDUP(H4/I4,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="25" t="n">
+        <f aca="false">N4-L3</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="6"/>
+      <c r="N4" s="26" t="n">
+        <f aca="false">MIN(Q4,Q10)</f>
+        <v>6</v>
+      </c>
+      <c r="O4" s="27"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="25" t="n">
+        <f aca="false">S4-Q3</f>
+        <v>6</v>
+      </c>
+      <c r="R4" s="6"/>
+      <c r="S4" s="26" t="n">
+        <f aca="false">V4</f>
+        <v>34</v>
+      </c>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="25" t="n">
+        <f aca="false">X4-V3</f>
+        <v>34</v>
+      </c>
+      <c r="W4" s="6"/>
+      <c r="X4" s="26" t="n">
+        <f aca="false">AA4</f>
+        <v>54</v>
+      </c>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="25" t="n">
+        <f aca="false">AC4-AA3</f>
+        <v>54</v>
+      </c>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="26" t="n">
+        <f aca="false">AF4</f>
+        <v>66</v>
+      </c>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="25" t="n">
+        <f aca="false">AH4-AF3</f>
+        <v>66</v>
+      </c>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="26" t="n">
+        <f aca="false">AK4</f>
+        <v>69</v>
+      </c>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="25" t="n">
+        <f aca="false">AM4-AK3</f>
+        <v>69</v>
+      </c>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="26" t="n">
+        <f aca="false">AM1</f>
+        <v>78</v>
+      </c>
+      <c r="AN4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <f aca="false">ROUNDUP(H5/I5,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="29"/>
+      <c r="AE5" s="30"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <f aca="false">100%-I5</f>
+        <v>0.75</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <f aca="false">ROUNDUP(H6/I6,0)</f>
+        <v>12</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="29"/>
+      <c r="AE6" s="30"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <f aca="false">ROUNDUP(H7/I7,0)</f>
+        <v>12</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="29"/>
+      <c r="Q7" s="7" t="n">
+        <f aca="false">N1</f>
+        <v>6</v>
+      </c>
+      <c r="R7" s="6"/>
+      <c r="S7" s="8" t="n">
+        <f aca="false">Q9+Q7</f>
+        <v>12</v>
+      </c>
+      <c r="V7" s="7" t="n">
+        <f aca="false">S7</f>
+        <v>12</v>
+      </c>
+      <c r="W7" s="6"/>
+      <c r="X7" s="8" t="n">
+        <f aca="false">V9+V7</f>
+        <v>24</v>
+      </c>
+      <c r="AA7" s="7" t="n">
+        <f aca="false">X7</f>
+        <v>24</v>
+      </c>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="8" t="n">
+        <f aca="false">AA9+AA7</f>
+        <v>34</v>
+      </c>
+      <c r="AE7" s="30"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="4"/>
-      <c r="X1" s="6" t="n">
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <f aca="false">ROUNDUP(H8/I8,0)</f>
+        <v>3</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="O8" s="29"/>
+      <c r="Q8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="V8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="AA8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AE8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <f aca="false">100%-I7</f>
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <f aca="false">ROUNDUP(H9/I9,0)</f>
+        <v>10</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="19" t="n">
+        <f aca="false">J4</f>
+        <v>6</v>
+      </c>
+      <c r="R9" s="20" t="n">
+        <f aca="false">S10-S7</f>
+        <v>32</v>
+      </c>
+      <c r="S9" s="21"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="19" t="n">
+        <f aca="false">J6</f>
+        <v>12</v>
+      </c>
+      <c r="W9" s="20" t="n">
+        <f aca="false">X10-X7</f>
+        <v>32</v>
+      </c>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="19" t="n">
+        <f aca="false">J9</f>
+        <v>10</v>
+      </c>
+      <c r="AB9" s="20" t="n">
+        <f aca="false">AC10-AC7</f>
+        <v>32</v>
+      </c>
+      <c r="AC9" s="21"/>
+      <c r="AD9" s="23"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <f aca="false">ROUNDUP(H10/I10,0)</f>
+        <v>9</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="Q10" s="25" t="n">
+        <f aca="false">S10-Q9</f>
+        <v>38</v>
+      </c>
+      <c r="R10" s="6"/>
+      <c r="S10" s="26" t="n">
+        <f aca="false">V10</f>
+        <v>44</v>
+      </c>
+      <c r="V10" s="25" t="n">
+        <f aca="false">X10-V9</f>
+        <v>44</v>
+      </c>
+      <c r="W10" s="6"/>
+      <c r="X10" s="26" t="n">
+        <f aca="false">AA10</f>
+        <v>56</v>
+      </c>
+      <c r="AA10" s="25" t="n">
+        <f aca="false">AC10-AA9</f>
+        <v>56</v>
+      </c>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="26" t="n">
+        <f aca="false">AF4</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF16" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="6" t="n">
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="4"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG2" s="11"/>
-      <c r="AH2" s="11"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL2" s="11"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="14" t="n">
-        <f aca="false">VLOOKUP(Q2,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="S3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="14" t="n">
-        <f aca="false">VLOOKUP(V2,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="W3" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="X3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="14" t="n">
-        <f aca="false">VLOOKUP(AA2,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC3" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="18"/>
-      <c r="AF3" s="14" t="n">
-        <f aca="false">VLOOKUP(AF2,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="AG3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="17"/>
-      <c r="AJ3" s="17"/>
-      <c r="AK3" s="14" t="n">
-        <f aca="false">VLOOKUP(AK2,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="AL3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="O4" s="21"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG4" s="4"/>
-      <c r="AH4" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AN4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="23"/>
-      <c r="AE5" s="24"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="23"/>
-      <c r="AE6" s="24"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="23"/>
-      <c r="Q7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" s="4"/>
-      <c r="X7" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA7" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE7" s="24"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="O8" s="23"/>
-      <c r="Q8" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="V8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="AA8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AE8" s="24"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="14" t="n">
-        <f aca="false">VLOOKUP(Q8,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="R9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="14" t="n">
-        <f aca="false">VLOOKUP(V8,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="14" t="n">
-        <f aca="false">VLOOKUP(AA8,$A$2:$J$10,8)</f>
-        <v>0</v>
-      </c>
-      <c r="AB9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="17"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" s="4"/>
-      <c r="Q10" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" s="4"/>
-      <c r="S10" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA10" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="20" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4"/>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF16" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
-      <c r="AB31" s="4"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="4"/>
-      <c r="AE31" s="4"/>
-      <c r="AF31" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
       <c r="K35" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="L35" s="26" t="s">
+      <c r="L35" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
       <c r="S35" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="T35" s="26" t="s">
+      <c r="T35" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="U35" s="26"/>
-      <c r="V35" s="26"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="26"/>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="26"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="26"/>
-      <c r="AD35" s="26"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="32"/>
+      <c r="AA35" s="32"/>
+      <c r="AB35" s="32"/>
+      <c r="AC35" s="32"/>
+      <c r="AD35" s="32"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="34" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28"/>
-      <c r="C38" s="28"/>
+      <c r="A38" s="34"/>
+      <c r="C38" s="34"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="28"/>
-      <c r="C39" s="28"/>
+      <c r="A39" s="34"/>
+      <c r="C39" s="34"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28"/>
-      <c r="C40" s="28"/>
+      <c r="A40" s="34"/>
+      <c r="C40" s="34"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="28"/>
-      <c r="C41" s="28"/>
+      <c r="A41" s="34"/>
+      <c r="C41" s="34"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28"/>
-      <c r="C42" s="28"/>
+      <c r="A42" s="34"/>
+      <c r="C42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28"/>
-      <c r="C43" s="28"/>
+      <c r="A43" s="34"/>
+      <c r="C43" s="34"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="28"/>
-      <c r="C44" s="28"/>
+      <c r="A44" s="34"/>
+      <c r="C44" s="34"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="28"/>
-      <c r="C45" s="28"/>
+      <c r="A45" s="34"/>
+      <c r="C45" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1818,7 +1930,7 @@
     <mergeCell ref="A37:A45"/>
     <mergeCell ref="C37:C45"/>
   </mergeCells>
-  <conditionalFormatting sqref="B35 M3 R3 W3 AB3 AG3 AL3 AB9 W9 R9">
+  <conditionalFormatting sqref="B35 M3 R3 R9 W9 W3 AB3 AB9 AG3 AL3">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1845,517 +1957,517 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="29" t="s">
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="39"/>
+      <c r="E2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="1" t="n">
+      <c r="G2" s="16"/>
+      <c r="H2" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="1" t="n">
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="10" t="s">
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="1" t="n">
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="1" t="n">
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="1" t="n">
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="2" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="6" t="n">
+      <c r="B9" s="6"/>
+      <c r="C9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="6"/>
+      <c r="H9" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="6" t="n">
+      <c r="L9" s="6"/>
+      <c r="M9" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="P9" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="6" t="n">
+      <c r="Q9" s="6"/>
+      <c r="R9" s="8" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="F10" s="11" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="F10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="K10" s="11" t="s">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="K10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="P10" s="11" t="s">
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="P10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="19" t="n">
         <f aca="false" t="array" ref="A11:A11">VLOOKUP(A10,$A$2:$H$10,8)</f>
         <v>6</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="19" t="n">
         <f aca="false" t="array" ref="F11:F11">VLOOKUP(F10,$A$2:$H$10,8)</f>
         <v>7</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="19" t="n">
         <f aca="false" t="array" ref="K11:K11">VLOOKUP(K10,$A$2:$H$10,8)</f>
         <v>5</v>
       </c>
-      <c r="L11" s="15" t="n">
+      <c r="L11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="15" t="n">
+      <c r="M11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="19" t="n">
         <f aca="false" t="array" ref="P11:P11">VLOOKUP(P10,$A$2:$H$10,8)</f>
         <v>9</v>
       </c>
-      <c r="Q11" s="15" t="n">
+      <c r="Q11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="15"/>
+      <c r="R11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="20" t="n">
+      <c r="B12" s="6"/>
+      <c r="C12" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="20" t="n">
+      <c r="G12" s="6"/>
+      <c r="H12" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="K12" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="20" t="n">
+      <c r="L12" s="6"/>
+      <c r="M12" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="P12" s="19" t="n">
+      <c r="P12" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="20" t="n">
+      <c r="Q12" s="6"/>
+      <c r="R12" s="26" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="6" t="n">
+      <c r="G15" s="6"/>
+      <c r="H15" s="8" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="19" t="n">
         <f aca="false" t="array" ref="F17:F17">VLOOKUP(F16,$A$2:$H$10,8)</f>
         <v>4</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="21" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="20" t="n">
+      <c r="G18" s="6"/>
+      <c r="H18" s="26" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="32"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
+      <c r="A50" s="40"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="41"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="32"/>
-      <c r="B51" s="34" t="s">
+      <c r="A51" s="40"/>
+      <c r="B51" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34" t="s">
+      <c r="C51" s="42"/>
+      <c r="D51" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="33"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="41"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="32"/>
-      <c r="B52" s="35" t="s">
+      <c r="A52" s="40"/>
+      <c r="B52" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="36" t="s">
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="33"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="41"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="32"/>
-      <c r="B53" s="37" t="s">
+      <c r="A53" s="40"/>
+      <c r="B53" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="38" t="s">
+      <c r="C53" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="37" t="s">
+      <c r="D53" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="33"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="41"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="32"/>
-      <c r="B54" s="34" t="s">
+      <c r="A54" s="40"/>
+      <c r="B54" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34" t="s">
+      <c r="C54" s="42"/>
+      <c r="D54" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="34"/>
-      <c r="I54" s="34"/>
-      <c r="J54" s="34"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="33"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="41"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="32"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="33"/>
+      <c r="A55" s="40"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="41"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="32"/>
-      <c r="B56" s="39" t="s">
+      <c r="A56" s="40"/>
+      <c r="B56" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="40" t="s">
+      <c r="C56" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="33"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
+      <c r="L56" s="41"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32"/>
-      <c r="B57" s="39" t="s">
+      <c r="A57" s="40"/>
+      <c r="B57" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C57" s="40" t="s">
+      <c r="C57" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="33"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
+      <c r="L57" s="41"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="32"/>
-      <c r="B58" s="39" t="s">
+      <c r="A58" s="40"/>
+      <c r="B58" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="40" t="s">
+      <c r="C58" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="33"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
+      <c r="L58" s="41"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="32"/>
-      <c r="B59" s="39" t="s">
+      <c r="A59" s="40"/>
+      <c r="B59" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="40" t="s">
+      <c r="C59" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="D59" s="40"/>
-      <c r="E59" s="40"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="33"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
+      <c r="L59" s="41"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="32"/>
-      <c r="B60" s="37" t="s">
+      <c r="A60" s="40"/>
+      <c r="B60" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="40" t="s">
+      <c r="C60" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="40"/>
-      <c r="L60" s="33"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
+      <c r="L60" s="41"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="32"/>
-      <c r="B61" s="38" t="s">
+      <c r="A61" s="40"/>
+      <c r="B61" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="40" t="s">
+      <c r="C61" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="D61" s="40"/>
-      <c r="E61" s="40"/>
-      <c r="F61" s="40"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="40"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="40"/>
-      <c r="K61" s="40"/>
-      <c r="L61" s="33"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
+      <c r="L61" s="41"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="32"/>
-      <c r="B62" s="41" t="s">
+      <c r="A62" s="40"/>
+      <c r="B62" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="33" t="s">
+      <c r="C62" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="33"/>
-      <c r="L62" s="33"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
+      <c r="K62" s="41"/>
+      <c r="L62" s="41"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="32"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
+      <c r="A63" s="40"/>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="41"/>
+      <c r="K63" s="41"/>
+      <c r="L63" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="39">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">C</t>
   </si>
   <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
     <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
   </si>
   <si>
     <t xml:space="preserve">E</t>
@@ -334,7 +334,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -429,6 +429,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1039,51 +1043,42 @@
       <c r="R1" s="6"/>
       <c r="S1" s="8" t="n">
         <f aca="false">Q3+Q1</f>
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="T1" s="6"/>
       <c r="U1" s="6"/>
-      <c r="V1" s="7" t="n">
-        <f aca="false">S1</f>
-        <v>34</v>
-      </c>
-      <c r="W1" s="6"/>
-      <c r="X1" s="8" t="n">
-        <f aca="false">V3+V1</f>
-        <v>54</v>
-      </c>
       <c r="Y1" s="6"/>
       <c r="Z1" s="6"/>
       <c r="AA1" s="7" t="n">
-        <f aca="false">X1</f>
-        <v>54</v>
+        <f aca="false">S1</f>
+        <v>26</v>
       </c>
       <c r="AB1" s="6"/>
       <c r="AC1" s="8" t="n">
         <f aca="false">AA3+AA1</f>
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AD1" s="6"/>
       <c r="AE1" s="6"/>
       <c r="AF1" s="7" t="n">
         <f aca="false">MAX(AC1,AC7)</f>
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="AG1" s="6"/>
       <c r="AH1" s="8" t="n">
         <f aca="false">AF3+AF1</f>
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
       <c r="AK1" s="7" t="n">
         <f aca="false">AH1</f>
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="AL1" s="6"/>
       <c r="AM1" s="8" t="n">
         <f aca="false">AK3+AK1</f>
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AN1" s="6"/>
     </row>
@@ -1130,35 +1125,30 @@
       <c r="S2" s="14"/>
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
-      <c r="V2" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
       <c r="AA2" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB2" s="14"/>
       <c r="AC2" s="14"/>
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
       <c r="AF2" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" s="14"/>
       <c r="AH2" s="14"/>
       <c r="AI2" s="6"/>
       <c r="AJ2" s="6"/>
       <c r="AK2" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" s="14"/>
       <c r="AM2" s="14"/>
       <c r="AN2" s="6"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1168,7 +1158,7 @@
       <c r="C3" s="16"/>
       <c r="D3" s="17"/>
       <c r="E3" s="16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -1176,11 +1166,11 @@
         <v>7</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="J3" s="9" t="n">
         <f aca="false">ROUNDUP(H3/I3,0)</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="19" t="n">
@@ -1196,37 +1186,31 @@
       <c r="P3" s="23"/>
       <c r="Q3" s="19" t="n">
         <f aca="false">J3</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="R3" s="20" t="n">
         <f aca="false">S4-S1</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S3" s="21"/>
       <c r="T3" s="23"/>
       <c r="U3" s="23"/>
-      <c r="V3" s="19" t="n">
-        <f aca="false">J5</f>
-        <v>20</v>
-      </c>
-      <c r="W3" s="20" t="n">
-        <f aca="false">X4-X1</f>
-        <v>0</v>
-      </c>
-      <c r="X3" s="21"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
       <c r="Y3" s="23"/>
       <c r="Z3" s="23"/>
       <c r="AA3" s="19" t="n">
         <f aca="false">J7</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AB3" s="20" t="n">
         <f aca="false">AC4-AC1</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC3" s="21"/>
       <c r="AD3" s="23"/>
-      <c r="AE3" s="24"/>
+      <c r="AE3" s="25"/>
       <c r="AF3" s="19" t="n">
         <f aca="false">J8</f>
         <v>3</v>
@@ -1268,109 +1252,87 @@
       </c>
       <c r="I4" s="18" t="n">
         <f aca="false">100%-I3</f>
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="J4" s="9" t="n">
         <f aca="false">ROUNDUP(H4/I4,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="25" t="n">
+      <c r="L4" s="26" t="n">
         <f aca="false">N4-L3</f>
         <v>0</v>
       </c>
       <c r="M4" s="6"/>
-      <c r="N4" s="26" t="n">
+      <c r="N4" s="27" t="n">
         <f aca="false">MIN(Q4,Q10)</f>
         <v>6</v>
       </c>
-      <c r="O4" s="27"/>
+      <c r="O4" s="28"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="25" t="n">
+      <c r="Q4" s="26" t="n">
         <f aca="false">S4-Q3</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R4" s="6"/>
-      <c r="S4" s="26" t="n">
-        <f aca="false">V4</f>
-        <v>34</v>
+      <c r="S4" s="27" t="n">
+        <f aca="false">AA4</f>
+        <v>29</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
-      <c r="V4" s="25" t="n">
-        <f aca="false">X4-V3</f>
-        <v>34</v>
-      </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="26" t="n">
-        <f aca="false">AA4</f>
-        <v>54</v>
-      </c>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
-      <c r="AA4" s="25" t="n">
+      <c r="AA4" s="26" t="n">
         <f aca="false">AC4-AA3</f>
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="AB4" s="6"/>
-      <c r="AC4" s="26" t="n">
+      <c r="AC4" s="27" t="n">
         <f aca="false">AF4</f>
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="AD4" s="6"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="25" t="n">
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="26" t="n">
         <f aca="false">AH4-AF3</f>
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="AG4" s="6"/>
-      <c r="AH4" s="26" t="n">
+      <c r="AH4" s="27" t="n">
         <f aca="false">AK4</f>
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="AI4" s="6"/>
       <c r="AJ4" s="6"/>
-      <c r="AK4" s="25" t="n">
+      <c r="AK4" s="26" t="n">
         <f aca="false">AM4-AK3</f>
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="AL4" s="6"/>
-      <c r="AM4" s="26" t="n">
+      <c r="AM4" s="27" t="n">
         <f aca="false">AM1</f>
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AN4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="16"/>
       <c r="D5" s="17"/>
-      <c r="E5" s="16" t="s">
-        <v>11</v>
-      </c>
+      <c r="E5" s="16"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-      <c r="H5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <f aca="false">ROUNDUP(H5/I5,0)</f>
-        <v>20</v>
-      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="9"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="29"/>
-      <c r="AE5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="AE5" s="31"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -1390,31 +1352,31 @@
         <v>9</v>
       </c>
       <c r="I6" s="18" t="n">
-        <f aca="false">100%-I5</f>
-        <v>0.75</v>
+        <f aca="false">100%-I3</f>
+        <v>0.65</v>
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">ROUNDUP(H6/I6,0)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="29"/>
-      <c r="AE6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="AE6" s="31"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="17"/>
       <c r="E7" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
@@ -1422,17 +1384,18 @@
         <v>3</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>0.25</v>
+        <f aca="false">I3</f>
+        <v>0.35</v>
       </c>
       <c r="J7" s="9" t="n">
         <f aca="false">ROUNDUP(H7/I7,0)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="29"/>
+      <c r="O7" s="30"/>
       <c r="Q7" s="7" t="n">
         <f aca="false">N1</f>
         <v>6</v>
@@ -1440,39 +1403,39 @@
       <c r="R7" s="6"/>
       <c r="S7" s="8" t="n">
         <f aca="false">Q9+Q7</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V7" s="7" t="n">
         <f aca="false">S7</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W7" s="6"/>
       <c r="X7" s="8" t="n">
         <f aca="false">V9+V7</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA7" s="7" t="n">
         <f aca="false">X7</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB7" s="6"/>
       <c r="AC7" s="8" t="n">
         <f aca="false">AA9+AA7</f>
-        <v>34</v>
-      </c>
-      <c r="AE7" s="30"/>
+        <v>38</v>
+      </c>
+      <c r="AE7" s="31"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="12"/>
       <c r="E8" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
@@ -1487,7 +1450,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="6"/>
-      <c r="O8" s="29"/>
+      <c r="O8" s="30"/>
       <c r="Q8" s="14" t="s">
         <v>9</v>
       </c>
@@ -1503,7 +1466,7 @@
       </c>
       <c r="AB8" s="14"/>
       <c r="AC8" s="14"/>
-      <c r="AE8" s="30"/>
+      <c r="AE8" s="31"/>
     </row>
     <row r="9" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -1515,7 +1478,7 @@
       <c r="C9" s="16"/>
       <c r="D9" s="17"/>
       <c r="E9" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
@@ -1523,54 +1486,54 @@
         <v>7</v>
       </c>
       <c r="I9" s="18" t="n">
-        <f aca="false">100%-I7</f>
-        <v>0.75</v>
+        <f aca="false">100%-I3</f>
+        <v>0.65</v>
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">ROUNDUP(H9/I9,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" s="6"/>
       <c r="P9" s="23"/>
       <c r="Q9" s="19" t="n">
         <f aca="false">J4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R9" s="20" t="n">
         <f aca="false">S10-S7</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="S9" s="21"/>
       <c r="T9" s="23"/>
       <c r="U9" s="23"/>
       <c r="V9" s="19" t="n">
         <f aca="false">J6</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W9" s="20" t="n">
         <f aca="false">X10-X7</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="X9" s="21"/>
       <c r="Y9" s="23"/>
       <c r="Z9" s="23"/>
       <c r="AA9" s="19" t="n">
         <f aca="false">J9</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB9" s="20" t="n">
         <f aca="false">AC10-AC7</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="21"/>
       <c r="AD9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>15</v>
@@ -1590,32 +1553,32 @@
         <v>9</v>
       </c>
       <c r="K10" s="6"/>
-      <c r="Q10" s="25" t="n">
+      <c r="Q10" s="26" t="n">
         <f aca="false">S10-Q9</f>
+        <v>6</v>
+      </c>
+      <c r="R10" s="6"/>
+      <c r="S10" s="27" t="n">
+        <f aca="false">V10</f>
+        <v>13</v>
+      </c>
+      <c r="V10" s="26" t="n">
+        <f aca="false">X10-V9</f>
+        <v>13</v>
+      </c>
+      <c r="W10" s="6"/>
+      <c r="X10" s="27" t="n">
+        <f aca="false">AA10</f>
+        <v>27</v>
+      </c>
+      <c r="AA10" s="26" t="n">
+        <f aca="false">AC10-AA9</f>
+        <v>27</v>
+      </c>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="27" t="n">
+        <f aca="false">AF4</f>
         <v>38</v>
-      </c>
-      <c r="R10" s="6"/>
-      <c r="S10" s="26" t="n">
-        <f aca="false">V10</f>
-        <v>44</v>
-      </c>
-      <c r="V10" s="25" t="n">
-        <f aca="false">X10-V9</f>
-        <v>44</v>
-      </c>
-      <c r="W10" s="6"/>
-      <c r="X10" s="26" t="n">
-        <f aca="false">AA10</f>
-        <v>56</v>
-      </c>
-      <c r="AA10" s="25" t="n">
-        <f aca="false">AC10-AA9</f>
-        <v>56</v>
-      </c>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="26" t="n">
-        <f aca="false">AF4</f>
-        <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1627,7 +1590,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="31"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
@@ -1659,10 +1622,19 @@
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="6"/>
+      <c r="G12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <f aca="false">G12/(H12*I12)</f>
+        <v>5</v>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -1742,7 +1714,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-      <c r="I31" s="31"/>
+      <c r="I31" s="32"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
@@ -1775,15 +1747,15 @@
       <c r="C33" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
@@ -1791,129 +1763,128 @@
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
     </row>
     <row r="35" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
       <c r="K35" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="L35" s="32" t="s">
+      <c r="L35" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
       <c r="S35" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="T35" s="32" t="s">
+      <c r="T35" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="32"/>
-      <c r="Y35" s="32"/>
-      <c r="Z35" s="32"/>
-      <c r="AA35" s="32"/>
-      <c r="AB35" s="32"/>
-      <c r="AC35" s="32"/>
-      <c r="AD35" s="32"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33"/>
+      <c r="AC35" s="33"/>
+      <c r="AD35" s="33"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="26" t="s">
         <v>27</v>
       </c>
       <c r="B36" s="6"/>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="35" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34"/>
-      <c r="C38" s="34"/>
+      <c r="A38" s="35"/>
+      <c r="C38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="34"/>
-      <c r="C39" s="34"/>
+      <c r="A39" s="35"/>
+      <c r="C39" s="35"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="34"/>
-      <c r="C40" s="34"/>
+      <c r="A40" s="35"/>
+      <c r="C40" s="35"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="34"/>
-      <c r="C41" s="34"/>
+      <c r="A41" s="35"/>
+      <c r="C41" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34"/>
-      <c r="C42" s="34"/>
+      <c r="A42" s="35"/>
+      <c r="C42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="34"/>
-      <c r="C43" s="34"/>
+      <c r="A43" s="35"/>
+      <c r="C43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34"/>
-      <c r="C44" s="34"/>
+      <c r="A44" s="35"/>
+      <c r="C44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="34"/>
-      <c r="C45" s="34"/>
+      <c r="A45" s="35"/>
+      <c r="C45" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="V2:X2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AF2:AH2"/>
     <mergeCell ref="AK2:AM2"/>
@@ -1930,7 +1901,7 @@
     <mergeCell ref="A37:A45"/>
     <mergeCell ref="C37:C45"/>
   </mergeCells>
-  <conditionalFormatting sqref="B35 M3 R3 R9 W9 W3 AB3 AB9 AG3 AL3">
+  <conditionalFormatting sqref="B35 M3 R3 R9 W9 AB3 AB9 AG3 AL3">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1960,31 +1931,31 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="39"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="16" t="s">
         <v>8</v>
       </c>
@@ -2006,7 +1977,7 @@
       <c r="C3" s="16"/>
       <c r="D3" s="17"/>
       <c r="E3" s="16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -2024,7 +1995,7 @@
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
@@ -2034,7 +2005,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>8</v>
@@ -2057,13 +2028,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="17"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
       <c r="H6" s="2" t="n">
         <v>9</v>
       </c>
@@ -2110,7 +2081,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="14"/>
       <c r="K10" s="14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
@@ -2161,32 +2132,32 @@
       <c r="R11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <v>0</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <v>6</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="26" t="n">
+      <c r="H12" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="K12" s="25" t="n">
+      <c r="K12" s="26" t="n">
         <v>13</v>
       </c>
       <c r="L12" s="6"/>
-      <c r="M12" s="26" t="n">
+      <c r="M12" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="P12" s="25" t="n">
+      <c r="P12" s="26" t="n">
         <v>18</v>
       </c>
       <c r="Q12" s="6"/>
-      <c r="R12" s="26" t="n">
+      <c r="R12" s="27" t="n">
         <v>27</v>
       </c>
     </row>
@@ -2219,255 +2190,255 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>9</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="26" t="n">
+      <c r="H18" s="27" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="40"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="40"/>
-      <c r="B51" s="42" t="s">
+      <c r="A51" s="41"/>
+      <c r="B51" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42" t="s">
+      <c r="C51" s="43"/>
+      <c r="D51" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
-      <c r="K51" s="42"/>
-      <c r="L51" s="41"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="43"/>
+      <c r="L51" s="42"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="40"/>
-      <c r="B52" s="43" t="s">
+      <c r="A52" s="41"/>
+      <c r="B52" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="44" t="s">
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="42"/>
-      <c r="L52" s="41"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="45"/>
+      <c r="I52" s="45"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="43"/>
+      <c r="L52" s="42"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="40"/>
-      <c r="B53" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="46" t="s">
+      <c r="A53" s="41"/>
+      <c r="B53" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="45" t="s">
+      <c r="D53" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="42"/>
-      <c r="K53" s="42"/>
-      <c r="L53" s="41"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="43"/>
+      <c r="H53" s="43"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="42"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="40"/>
-      <c r="B54" s="42" t="s">
+      <c r="A54" s="41"/>
+      <c r="B54" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42" t="s">
+      <c r="C54" s="43"/>
+      <c r="D54" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="42"/>
-      <c r="J54" s="42"/>
-      <c r="K54" s="42"/>
-      <c r="L54" s="41"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+      <c r="L54" s="42"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="40"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="42"/>
-      <c r="K55" s="42"/>
-      <c r="L55" s="41"/>
+      <c r="A55" s="41"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
+      <c r="K55" s="43"/>
+      <c r="L55" s="42"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="40"/>
-      <c r="B56" s="47" t="s">
+      <c r="A56" s="41"/>
+      <c r="B56" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="48" t="s">
+      <c r="C56" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
-      <c r="L56" s="41"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
+      <c r="L56" s="42"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="40"/>
-      <c r="B57" s="47" t="s">
+      <c r="A57" s="41"/>
+      <c r="B57" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="C57" s="48" t="s">
+      <c r="C57" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
-      <c r="L57" s="41"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="42"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40"/>
-      <c r="B58" s="47" t="s">
+      <c r="A58" s="41"/>
+      <c r="B58" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="48" t="s">
+      <c r="C58" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
-      <c r="L58" s="41"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+      <c r="L58" s="42"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40"/>
-      <c r="B59" s="47" t="s">
+      <c r="A59" s="41"/>
+      <c r="B59" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="48" t="s">
+      <c r="C59" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
-      <c r="L59" s="41"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="49"/>
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="42"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="40"/>
-      <c r="B60" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" s="48" t="s">
+      <c r="A60" s="41"/>
+      <c r="B60" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="48"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
-      <c r="L60" s="41"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="42"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="40"/>
-      <c r="B61" s="46" t="s">
+      <c r="A61" s="41"/>
+      <c r="B61" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="48" t="s">
+      <c r="C61" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
-      <c r="L61" s="41"/>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="49"/>
+      <c r="J61" s="49"/>
+      <c r="K61" s="49"/>
+      <c r="L61" s="42"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="40"/>
-      <c r="B62" s="49" t="s">
+      <c r="A62" s="41"/>
+      <c r="B62" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="41" t="s">
+      <c r="C62" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="41"/>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
-      <c r="L62" s="41"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="L62" s="42"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="40"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="41"/>
+      <c r="A63" s="41"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
+      <c r="L63" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="15">

--- a/Übungen/01_Netzplan_Übung.xlsx
+++ b/Übungen/01_Netzplan_Übung.xlsx
@@ -5,10 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle2" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Übung1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Tabelle3" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -993,7 +993,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AN45"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.74"/>
@@ -1922,7 +1922,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R63"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="1" style="0" width="3.83"/>
   </cols>
